--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894461</v>
+        <v>129894447</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -703,17 +703,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493611</v>
+        <v>493899</v>
       </c>
       <c r="R2" t="n">
-        <v>7035450</v>
+        <v>7035614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,8 +770,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894447</v>
+        <v>129894461</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -805,28 +842,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493899</v>
+        <v>493611</v>
       </c>
       <c r="R3" t="n">
-        <v>7035614</v>
+        <v>7035450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,34 +898,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,7 +919,7 @@
         <v>129894437</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129894458</v>
+        <v>129894470</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493261</v>
+        <v>493838</v>
       </c>
       <c r="R5" t="n">
-        <v>7035114</v>
+        <v>7035688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894470</v>
+        <v>129894458</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493261</v>
       </c>
       <c r="R6" t="n">
-        <v>7035688</v>
+        <v>7035114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1926,32 +1926,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894479</v>
+        <v>129894457</v>
       </c>
       <c r="B13" t="n">
-        <v>100969</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493970</v>
+        <v>493307</v>
       </c>
       <c r="R13" t="n">
-        <v>7035615</v>
+        <v>7035159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894457</v>
+        <v>129894479</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>100979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493307</v>
+        <v>493970</v>
       </c>
       <c r="R14" t="n">
-        <v>7035159</v>
+        <v>7035615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894439</v>
+        <v>129894452</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493917</v>
+        <v>493770</v>
       </c>
       <c r="R15" t="n">
-        <v>7035788</v>
+        <v>7035500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129894452</v>
+        <v>129894439</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493770</v>
+        <v>493917</v>
       </c>
       <c r="R16" t="n">
-        <v>7035500</v>
+        <v>7035788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,38 +2334,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894429</v>
+        <v>129894446</v>
       </c>
       <c r="B17" t="n">
-        <v>97651</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2373,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494017</v>
+        <v>493940</v>
       </c>
       <c r="R17" t="n">
-        <v>7035651</v>
+        <v>7035627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,6 +2418,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2424,6 +2436,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2441,45 +2473,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894446</v>
+        <v>129894429</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>97661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2487,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493940</v>
+        <v>494017</v>
       </c>
       <c r="R18" t="n">
-        <v>7035627</v>
+        <v>7035651</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,11 +2550,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2543,26 +2563,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
         <v>129894480</v>
       </c>
       <c r="B19" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894462</v>
+        <v>129894454</v>
       </c>
       <c r="B20" t="n">
         <v>79081</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493596</v>
+        <v>493694</v>
       </c>
       <c r="R20" t="n">
-        <v>7035472</v>
+        <v>7035412</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,7 +2798,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894454</v>
+        <v>129894462</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493694</v>
+        <v>493596</v>
       </c>
       <c r="R21" t="n">
-        <v>7035412</v>
+        <v>7035472</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3545,53 +3545,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894482</v>
+        <v>129894455</v>
       </c>
       <c r="B28" t="n">
-        <v>100969</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493912</v>
+        <v>493715</v>
       </c>
       <c r="R28" t="n">
-        <v>7035578</v>
+        <v>7035494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3628,7 +3620,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I ett relativt örtrikt stråk i granskog.</t>
+          <t>Rikligt och med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,14 +3629,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3661,45 +3647,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894455</v>
+        <v>129894482</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>100979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493715</v>
+        <v>493912</v>
       </c>
       <c r="R29" t="n">
-        <v>7035494</v>
+        <v>7035578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,7 +3730,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på flera granar.</t>
+          <t>I ett relativt örtrikt stråk i granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,8 +3739,14 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3763,45 +3763,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894463</v>
+        <v>129894428</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493634</v>
+        <v>494023</v>
       </c>
       <c r="R30" t="n">
-        <v>7035511</v>
+        <v>7035675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,7 +3845,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,8 +3854,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3865,7 +3898,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894450</v>
+        <v>129894464</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3900,10 +3933,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493823</v>
+        <v>493723</v>
       </c>
       <c r="R31" t="n">
-        <v>7035581</v>
+        <v>7035578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3973,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3967,52 +4000,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894428</v>
+        <v>129894450</v>
       </c>
       <c r="B32" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494023</v>
+        <v>493823</v>
       </c>
       <c r="R32" t="n">
-        <v>7035675</v>
+        <v>7035581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4049,7 +4075,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,34 +4084,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4102,7 +4102,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894464</v>
+        <v>129894463</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493723</v>
+        <v>493634</v>
       </c>
       <c r="R33" t="n">
-        <v>7035578</v>
+        <v>7035511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4327,7 +4327,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894459</v>
+        <v>129894472</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493464</v>
+        <v>493872</v>
       </c>
       <c r="R35" t="n">
-        <v>7035297</v>
+        <v>7035742</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4429,7 +4429,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894472</v>
+        <v>129894459</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493872</v>
+        <v>493464</v>
       </c>
       <c r="R36" t="n">
-        <v>7035742</v>
+        <v>7035297</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4633,10 +4633,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894467</v>
+        <v>129894431</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,34 +4644,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493793</v>
+        <v>493921</v>
       </c>
       <c r="R38" t="n">
-        <v>7035636</v>
+        <v>7035594</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,7 +4711,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4717,8 +4720,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4735,10 +4764,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894431</v>
+        <v>129894467</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4746,37 +4775,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493921</v>
+        <v>493793</v>
       </c>
       <c r="R39" t="n">
-        <v>7035594</v>
+        <v>7035636</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4813,7 +4839,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4822,34 +4848,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4869,7 +4869,7 @@
         <v>129894481</v>
       </c>
       <c r="B40" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894477</v>
+        <v>129894468</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494035</v>
+        <v>493808</v>
       </c>
       <c r="R41" t="n">
-        <v>7035664</v>
+        <v>7035662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>På flera granar och på bark av tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894468</v>
+        <v>129894469</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493808</v>
+        <v>493858</v>
       </c>
       <c r="R42" t="n">
-        <v>7035662</v>
+        <v>7035683</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På flera granar och på bark av tall.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,7 +5186,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894469</v>
+        <v>129894445</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493858</v>
+        <v>493904</v>
       </c>
       <c r="R43" t="n">
-        <v>7035683</v>
+        <v>7035660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,7 +5390,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894445</v>
+        <v>129894477</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493904</v>
+        <v>494035</v>
       </c>
       <c r="R45" t="n">
-        <v>7035660</v>
+        <v>7035664</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5937,53 +5937,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894483</v>
+        <v>129894465</v>
       </c>
       <c r="B50" t="n">
-        <v>100969</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493945</v>
+        <v>493746</v>
       </c>
       <c r="R50" t="n">
-        <v>7035601</v>
+        <v>7035617</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6018,20 +6010,19 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gott om bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6048,7 +6039,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894465</v>
+        <v>129894473</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -6083,10 +6074,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493746</v>
+        <v>493901</v>
       </c>
       <c r="R51" t="n">
-        <v>7035617</v>
+        <v>7035798</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6123,7 +6114,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gott om bålar på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6150,45 +6141,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894473</v>
+        <v>129894483</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>100979</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493901</v>
+        <v>493945</v>
       </c>
       <c r="R52" t="n">
-        <v>7035798</v>
+        <v>7035601</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6223,19 +6222,20 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6354,32 +6354,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894426</v>
+        <v>129894474</v>
       </c>
       <c r="B54" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493924</v>
+        <v>493922</v>
       </c>
       <c r="R54" t="n">
-        <v>7035590</v>
+        <v>7035751</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6456,32 +6456,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894474</v>
+        <v>129894426</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493922</v>
+        <v>493924</v>
       </c>
       <c r="R55" t="n">
-        <v>7035751</v>
+        <v>7035590</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6561,7 +6561,7 @@
         <v>129894438</v>
       </c>
       <c r="B56" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>129894436</v>
       </c>
       <c r="B57" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894447</v>
+        <v>129894437</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493899</v>
+        <v>493943</v>
       </c>
       <c r="R2" t="n">
-        <v>7035614</v>
+        <v>7035674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,26 +782,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894461</v>
+        <v>129894447</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,17 +827,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493611</v>
+        <v>493899</v>
       </c>
       <c r="R3" t="n">
-        <v>7035450</v>
+        <v>7035614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,8 +894,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,61 +938,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894437</v>
+        <v>129894461</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493943</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7035674</v>
+        <v>7035450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,14 +1022,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129894470</v>
+        <v>129894458</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493838</v>
+        <v>493261</v>
       </c>
       <c r="R5" t="n">
-        <v>7035688</v>
+        <v>7035114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894458</v>
+        <v>129894470</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493261</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>7035114</v>
+        <v>7035688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129894449</v>
+        <v>129894440</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493828</v>
+        <v>493988</v>
       </c>
       <c r="R7" t="n">
-        <v>7035639</v>
+        <v>7035698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129894440</v>
+        <v>129894449</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493988</v>
+        <v>493828</v>
       </c>
       <c r="R8" t="n">
-        <v>7035698</v>
+        <v>7035639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
         <v>129894427</v>
       </c>
       <c r="B9" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129894444</v>
+        <v>129894442</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,28 +1611,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493977</v>
+        <v>493963</v>
       </c>
       <c r="R10" t="n">
-        <v>7035653</v>
+        <v>7035733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1658,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt och ymnigt på många granar i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,34 +1667,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1722,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894442</v>
+        <v>129894444</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,17 +1713,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493963</v>
+        <v>493977</v>
       </c>
       <c r="R11" t="n">
-        <v>7035733</v>
+        <v>7035653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1771,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt och ymnigt på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,8 +1780,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894476</v>
+        <v>129894457</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494006</v>
+        <v>493307</v>
       </c>
       <c r="R12" t="n">
-        <v>7035657</v>
+        <v>7035159</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894457</v>
+        <v>129894476</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493307</v>
+        <v>494006</v>
       </c>
       <c r="R13" t="n">
-        <v>7035159</v>
+        <v>7035657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2031,7 @@
         <v>129894479</v>
       </c>
       <c r="B14" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129894452</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>129894439</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129894446</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>129894429</v>
       </c>
       <c r="B18" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>129894480</v>
       </c>
       <c r="B19" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894454</v>
+        <v>129894462</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493694</v>
+        <v>493596</v>
       </c>
       <c r="R20" t="n">
-        <v>7035412</v>
+        <v>7035472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,10 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894462</v>
+        <v>129894454</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493596</v>
+        <v>493694</v>
       </c>
       <c r="R21" t="n">
-        <v>7035472</v>
+        <v>7035412</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894423</v>
+        <v>129894451</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,41 +2911,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493910</v>
+        <v>493860</v>
       </c>
       <c r="R22" t="n">
-        <v>7035709</v>
+        <v>7035559</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2982,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i en samling granlågor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2991,34 +2984,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3035,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894451</v>
+        <v>129894423</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,34 +3013,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493860</v>
+        <v>493910</v>
       </c>
       <c r="R23" t="n">
-        <v>7035559</v>
+        <v>7035709</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,7 +3084,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I en upplyft granlåga i en samling granlågor.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,8 +3093,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3140,7 +3140,7 @@
         <v>129894453</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129894460</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129894475</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3443,45 +3443,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129894456</v>
+        <v>129894482</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>100983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493645</v>
+        <v>493912</v>
       </c>
       <c r="R27" t="n">
-        <v>7035420</v>
+        <v>7035578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3518,7 +3526,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i granskog.</t>
+          <t>I ett relativt örtrikt stråk i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3527,8 +3535,14 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3545,10 +3559,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894455</v>
+        <v>129894456</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,10 +3594,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493715</v>
+        <v>493645</v>
       </c>
       <c r="R28" t="n">
-        <v>7035494</v>
+        <v>7035420</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3620,7 +3634,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på flera granar.</t>
+          <t>Bland andra hänglavar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,53 +3661,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894482</v>
+        <v>129894455</v>
       </c>
       <c r="B29" t="n">
-        <v>100979</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493912</v>
+        <v>493715</v>
       </c>
       <c r="R29" t="n">
-        <v>7035578</v>
+        <v>7035494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3730,7 +3736,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I ett relativt örtrikt stråk i granskog.</t>
+          <t>Rikligt och med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,14 +3745,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3763,52 +3763,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894428</v>
+        <v>129894463</v>
       </c>
       <c r="B30" t="n">
-        <v>80215</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494023</v>
+        <v>493634</v>
       </c>
       <c r="R30" t="n">
-        <v>7035675</v>
+        <v>7035511</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3838,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,34 +3847,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3901,7 +3868,7 @@
         <v>129894464</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4003,7 +3970,7 @@
         <v>129894450</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,45 +4069,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894463</v>
+        <v>129894428</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493634</v>
+        <v>494023</v>
       </c>
       <c r="R33" t="n">
-        <v>7035511</v>
+        <v>7035675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,7 +4151,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,8 +4160,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4207,7 +4207,7 @@
         <v>129894432</v>
       </c>
       <c r="B34" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4327,10 +4327,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894472</v>
+        <v>129894459</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493872</v>
+        <v>493464</v>
       </c>
       <c r="R35" t="n">
-        <v>7035742</v>
+        <v>7035297</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4429,10 +4429,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894459</v>
+        <v>129894472</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493464</v>
+        <v>493872</v>
       </c>
       <c r="R36" t="n">
-        <v>7035297</v>
+        <v>7035742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4534,7 +4534,7 @@
         <v>129894471</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4633,37 +4633,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894431</v>
+        <v>129894481</v>
       </c>
       <c r="B38" t="n">
-        <v>80186</v>
+        <v>100983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4671,10 +4676,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493921</v>
+        <v>493990</v>
       </c>
       <c r="R38" t="n">
-        <v>7035594</v>
+        <v>7035652</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4727,26 +4732,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4767,7 +4752,7 @@
         <v>129894467</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4866,42 +4851,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894481</v>
+        <v>129894431</v>
       </c>
       <c r="B40" t="n">
-        <v>100979</v>
+        <v>80189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4909,10 +4889,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493990</v>
+        <v>493921</v>
       </c>
       <c r="R40" t="n">
-        <v>7035652</v>
+        <v>7035594</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4949,7 +4929,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,6 +4945,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894468</v>
+        <v>129894469</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493808</v>
+        <v>493858</v>
       </c>
       <c r="R41" t="n">
-        <v>7035662</v>
+        <v>7035683</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På flera granar och på bark av tall.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,10 +5084,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894469</v>
+        <v>129894445</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493858</v>
+        <v>493904</v>
       </c>
       <c r="R42" t="n">
-        <v>7035683</v>
+        <v>7035660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,10 +5186,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894445</v>
+        <v>129894448</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493904</v>
+        <v>493853</v>
       </c>
       <c r="R43" t="n">
-        <v>7035660</v>
+        <v>7035633</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>Hyfsat rikligt på gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,10 +5288,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894448</v>
+        <v>129894477</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493853</v>
+        <v>494035</v>
       </c>
       <c r="R44" t="n">
-        <v>7035633</v>
+        <v>7035664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på gran.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894477</v>
+        <v>129894468</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494035</v>
+        <v>493808</v>
       </c>
       <c r="R45" t="n">
-        <v>7035664</v>
+        <v>7035662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>På flera granar och på bark av tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5492,10 +5492,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894425</v>
+        <v>129894443</v>
       </c>
       <c r="B46" t="n">
-        <v>57896</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5503,50 +5503,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493632</v>
+        <v>493892</v>
       </c>
       <c r="R46" t="n">
-        <v>7035408</v>
+        <v>7035776</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5583,7 +5567,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
+          <t>På en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5594,11 +5578,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5615,10 +5594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894443</v>
+        <v>129894441</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5650,10 +5629,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493892</v>
+        <v>493967</v>
       </c>
       <c r="R47" t="n">
-        <v>7035776</v>
+        <v>7035717</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5690,7 +5669,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd.</t>
+          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5717,10 +5696,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894441</v>
+        <v>129894425</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>57895</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5728,34 +5707,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493967</v>
+        <v>493632</v>
       </c>
       <c r="R48" t="n">
-        <v>7035717</v>
+        <v>7035408</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
+          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5803,6 +5798,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5819,61 +5819,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129894433</v>
+        <v>129894473</v>
       </c>
       <c r="B49" t="n">
-        <v>58106</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493624</v>
+        <v>493901</v>
       </c>
       <c r="R49" t="n">
-        <v>7035496</v>
+        <v>7035798</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5908,6 +5892,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5916,11 +5905,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5940,7 +5924,7 @@
         <v>129894465</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,45 +6023,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894473</v>
+        <v>129894483</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>100983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493901</v>
+        <v>493945</v>
       </c>
       <c r="R51" t="n">
-        <v>7035798</v>
+        <v>7035601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6112,19 +6104,20 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6141,10 +6134,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894483</v>
+        <v>129894433</v>
       </c>
       <c r="B52" t="n">
-        <v>100979</v>
+        <v>58108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6152,42 +6145,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493945</v>
+        <v>493624</v>
       </c>
       <c r="R52" t="n">
-        <v>7035601</v>
+        <v>7035496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6228,7 +6229,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>129894466</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,32 +6354,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894474</v>
+        <v>129894426</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493922</v>
+        <v>493924</v>
       </c>
       <c r="R54" t="n">
-        <v>7035751</v>
+        <v>7035590</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6456,32 +6456,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894426</v>
+        <v>129894474</v>
       </c>
       <c r="B55" t="n">
-        <v>80215</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493924</v>
+        <v>493922</v>
       </c>
       <c r="R55" t="n">
-        <v>7035590</v>
+        <v>7035751</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6561,7 +6561,7 @@
         <v>129894438</v>
       </c>
       <c r="B56" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>129894436</v>
       </c>
       <c r="B57" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894437</v>
+        <v>129894447</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493943</v>
+        <v>493899</v>
       </c>
       <c r="R2" t="n">
-        <v>7035674</v>
+        <v>7035614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +777,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894447</v>
+        <v>129894461</v>
       </c>
       <c r="B3" t="n">
         <v>79084</v>
@@ -827,28 +842,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493899</v>
+        <v>493611</v>
       </c>
       <c r="R3" t="n">
-        <v>7035614</v>
+        <v>7035450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,34 +898,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -938,45 +916,61 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894461</v>
+        <v>129894437</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493943</v>
       </c>
       <c r="R4" t="n">
-        <v>7035450</v>
+        <v>7035674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,8 +1016,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894452</v>
+        <v>129894439</v>
       </c>
       <c r="B15" t="n">
         <v>79084</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493770</v>
+        <v>493917</v>
       </c>
       <c r="R15" t="n">
-        <v>7035500</v>
+        <v>7035788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,45 +2232,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129894439</v>
+        <v>129894429</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>97665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493917</v>
+        <v>494017</v>
       </c>
       <c r="R16" t="n">
-        <v>7035788</v>
+        <v>7035651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,19 +2309,20 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2334,7 +2339,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894446</v>
+        <v>129894452</v>
       </c>
       <c r="B17" t="n">
         <v>79084</v>
@@ -2362,28 +2367,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493940</v>
+        <v>493770</v>
       </c>
       <c r="R17" t="n">
-        <v>7035627</v>
+        <v>7035500</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,34 +2423,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2473,38 +2441,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894429</v>
+        <v>129894446</v>
       </c>
       <c r="B18" t="n">
-        <v>97665</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2512,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494017</v>
+        <v>493940</v>
       </c>
       <c r="R18" t="n">
-        <v>7035651</v>
+        <v>7035627</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2550,6 +2525,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2563,6 +2543,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894451</v>
+        <v>129894423</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>91602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2911,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493860</v>
+        <v>493910</v>
       </c>
       <c r="R22" t="n">
-        <v>7035559</v>
+        <v>7035709</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,7 +2982,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I en upplyft granlåga i en samling granlågor.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,8 +2991,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3002,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894423</v>
+        <v>129894451</v>
       </c>
       <c r="B23" t="n">
-        <v>91602</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,41 +3046,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493910</v>
+        <v>493860</v>
       </c>
       <c r="R23" t="n">
-        <v>7035709</v>
+        <v>7035559</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,7 +3110,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i en samling granlågor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,34 +3119,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3239,7 +3239,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894460</v>
+        <v>129894475</v>
       </c>
       <c r="B25" t="n">
         <v>79084</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493489</v>
+        <v>493953</v>
       </c>
       <c r="R25" t="n">
-        <v>7035303</v>
+        <v>7035683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129894475</v>
+        <v>129894460</v>
       </c>
       <c r="B26" t="n">
         <v>79084</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493953</v>
+        <v>493489</v>
       </c>
       <c r="R26" t="n">
-        <v>7035683</v>
+        <v>7035303</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,53 +3443,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129894482</v>
+        <v>129894456</v>
       </c>
       <c r="B27" t="n">
-        <v>100983</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493912</v>
+        <v>493645</v>
       </c>
       <c r="R27" t="n">
-        <v>7035578</v>
+        <v>7035420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3518,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I ett relativt örtrikt stråk i granskog.</t>
+          <t>Bland andra hänglavar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,14 +3527,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3559,7 +3545,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894456</v>
+        <v>129894455</v>
       </c>
       <c r="B28" t="n">
         <v>79084</v>
@@ -3594,10 +3580,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493645</v>
+        <v>493715</v>
       </c>
       <c r="R28" t="n">
-        <v>7035420</v>
+        <v>7035494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3634,7 +3620,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i granskog.</t>
+          <t>Rikligt och med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3661,45 +3647,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894455</v>
+        <v>129894482</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>100983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493715</v>
+        <v>493912</v>
       </c>
       <c r="R29" t="n">
-        <v>7035494</v>
+        <v>7035578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3736,7 +3730,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på flera granar.</t>
+          <t>I ett relativt örtrikt stråk i granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,8 +3739,14 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3763,45 +3763,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894463</v>
+        <v>129894428</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>80218</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493634</v>
+        <v>494023</v>
       </c>
       <c r="R30" t="n">
-        <v>7035511</v>
+        <v>7035675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,7 +3845,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,8 +3854,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3865,45 +3898,61 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894464</v>
+        <v>129894432</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493723</v>
+        <v>493967</v>
       </c>
       <c r="R31" t="n">
-        <v>7035578</v>
+        <v>7035617</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3989,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,6 +4000,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3967,7 +4021,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894450</v>
+        <v>129894463</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -4002,10 +4056,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493823</v>
+        <v>493634</v>
       </c>
       <c r="R32" t="n">
-        <v>7035581</v>
+        <v>7035511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,7 +4096,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4069,52 +4123,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894428</v>
+        <v>129894464</v>
       </c>
       <c r="B33" t="n">
-        <v>80218</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494023</v>
+        <v>493723</v>
       </c>
       <c r="R33" t="n">
-        <v>7035675</v>
+        <v>7035578</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4151,7 +4198,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,34 +4207,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4204,61 +4225,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894432</v>
+        <v>129894450</v>
       </c>
       <c r="B34" t="n">
-        <v>58108</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493967</v>
+        <v>493823</v>
       </c>
       <c r="R34" t="n">
-        <v>7035617</v>
+        <v>7035581</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4295,7 +4300,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4306,11 +4311,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4633,42 +4633,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894481</v>
+        <v>129894431</v>
       </c>
       <c r="B38" t="n">
-        <v>100983</v>
+        <v>80189</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4676,10 +4671,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493990</v>
+        <v>493921</v>
       </c>
       <c r="R38" t="n">
-        <v>7035652</v>
+        <v>7035594</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4716,7 +4711,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,6 +4727,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4749,45 +4764,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894467</v>
+        <v>129894481</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>100983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493793</v>
+        <v>493990</v>
       </c>
       <c r="R39" t="n">
-        <v>7035636</v>
+        <v>7035652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4824,7 +4847,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4833,8 +4856,14 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4851,10 +4880,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894431</v>
+        <v>129894467</v>
       </c>
       <c r="B40" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,37 +4891,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493921</v>
+        <v>493793</v>
       </c>
       <c r="R40" t="n">
-        <v>7035594</v>
+        <v>7035636</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4929,7 +4955,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4938,34 +4964,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894445</v>
+        <v>129894477</v>
       </c>
       <c r="B42" t="n">
         <v>79084</v>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493904</v>
+        <v>494035</v>
       </c>
       <c r="R42" t="n">
-        <v>7035660</v>
+        <v>7035664</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,7 +5186,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894448</v>
+        <v>129894445</v>
       </c>
       <c r="B43" t="n">
         <v>79084</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493853</v>
+        <v>493904</v>
       </c>
       <c r="R43" t="n">
-        <v>7035633</v>
+        <v>7035660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på gran.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,7 +5288,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894477</v>
+        <v>129894448</v>
       </c>
       <c r="B44" t="n">
         <v>79084</v>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494035</v>
+        <v>493853</v>
       </c>
       <c r="R44" t="n">
-        <v>7035664</v>
+        <v>7035633</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>Hyfsat rikligt på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129894473</v>
+        <v>129894465</v>
       </c>
       <c r="B49" t="n">
         <v>79084</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493901</v>
+        <v>493746</v>
       </c>
       <c r="R49" t="n">
-        <v>7035798</v>
+        <v>7035617</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Gott om bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894465</v>
+        <v>129894473</v>
       </c>
       <c r="B50" t="n">
         <v>79084</v>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493746</v>
+        <v>493901</v>
       </c>
       <c r="R50" t="n">
-        <v>7035617</v>
+        <v>7035798</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gott om bålar på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6023,10 +6023,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894483</v>
+        <v>129894433</v>
       </c>
       <c r="B51" t="n">
-        <v>100983</v>
+        <v>58108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6034,42 +6034,50 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493945</v>
+        <v>493624</v>
       </c>
       <c r="R51" t="n">
-        <v>7035601</v>
+        <v>7035496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6110,7 +6118,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6134,10 +6141,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894433</v>
+        <v>129894483</v>
       </c>
       <c r="B52" t="n">
-        <v>58108</v>
+        <v>100983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6145,50 +6152,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493624</v>
+        <v>493945</v>
       </c>
       <c r="R52" t="n">
-        <v>7035496</v>
+        <v>7035601</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,6 +6228,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129894438</v>
+        <v>129894436</v>
       </c>
       <c r="B56" t="n">
         <v>98794</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493981</v>
+        <v>493946</v>
       </c>
       <c r="R56" t="n">
-        <v>7035656</v>
+        <v>7035738</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6682,7 +6682,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894436</v>
+        <v>129894438</v>
       </c>
       <c r="B57" t="n">
         <v>98794</v>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493946</v>
+        <v>493981</v>
       </c>
       <c r="R57" t="n">
-        <v>7035738</v>
+        <v>7035656</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894447</v>
+        <v>129894437</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493899</v>
+        <v>493943</v>
       </c>
       <c r="R2" t="n">
-        <v>7035614</v>
+        <v>7035674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,26 +782,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894461</v>
+        <v>129894447</v>
       </c>
       <c r="B3" t="n">
         <v>79084</v>
@@ -842,17 +827,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493611</v>
+        <v>493899</v>
       </c>
       <c r="R3" t="n">
-        <v>7035450</v>
+        <v>7035614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,8 +894,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,61 +938,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894437</v>
+        <v>129894461</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493943</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7035674</v>
+        <v>7035450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,14 +1022,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -2130,45 +2130,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894439</v>
+        <v>129894480</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>100983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493917</v>
+        <v>493987</v>
       </c>
       <c r="R15" t="n">
-        <v>7035788</v>
+        <v>7035633</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,7 +2213,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,8 +2222,14 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2441,7 +2455,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894446</v>
+        <v>129894439</v>
       </c>
       <c r="B18" t="n">
         <v>79084</v>
@@ -2469,28 +2483,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493940</v>
+        <v>493917</v>
       </c>
       <c r="R18" t="n">
-        <v>7035627</v>
+        <v>7035788</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2530,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,34 +2539,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2580,42 +2557,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894480</v>
+        <v>129894446</v>
       </c>
       <c r="B19" t="n">
-        <v>100983</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2623,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493987</v>
+        <v>493940</v>
       </c>
       <c r="R19" t="n">
-        <v>7035633</v>
+        <v>7035627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,7 +2643,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,6 +2659,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894475</v>
+        <v>129894460</v>
       </c>
       <c r="B25" t="n">
         <v>79084</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493953</v>
+        <v>493489</v>
       </c>
       <c r="R25" t="n">
-        <v>7035683</v>
+        <v>7035303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129894460</v>
+        <v>129894475</v>
       </c>
       <c r="B26" t="n">
         <v>79084</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493489</v>
+        <v>493953</v>
       </c>
       <c r="R26" t="n">
-        <v>7035303</v>
+        <v>7035683</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3898,61 +3898,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894432</v>
+        <v>129894463</v>
       </c>
       <c r="B31" t="n">
-        <v>58108</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493967</v>
+        <v>493634</v>
       </c>
       <c r="R31" t="n">
-        <v>7035617</v>
+        <v>7035511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3989,7 +3973,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,11 +3984,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4021,7 +4000,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894463</v>
+        <v>129894464</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -4056,10 +4035,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493634</v>
+        <v>493723</v>
       </c>
       <c r="R32" t="n">
-        <v>7035511</v>
+        <v>7035578</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4096,7 +4075,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4123,7 +4102,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894464</v>
+        <v>129894450</v>
       </c>
       <c r="B33" t="n">
         <v>79084</v>
@@ -4158,10 +4137,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493723</v>
+        <v>493823</v>
       </c>
       <c r="R33" t="n">
-        <v>7035578</v>
+        <v>7035581</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4198,7 +4177,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4225,45 +4204,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894450</v>
+        <v>129894432</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493823</v>
+        <v>493967</v>
       </c>
       <c r="R34" t="n">
-        <v>7035581</v>
+        <v>7035617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4300,7 +4295,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4311,6 +4306,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4982,7 +4982,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894469</v>
+        <v>129894477</v>
       </c>
       <c r="B41" t="n">
         <v>79084</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493858</v>
+        <v>494035</v>
       </c>
       <c r="R41" t="n">
-        <v>7035683</v>
+        <v>7035664</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894477</v>
+        <v>129894469</v>
       </c>
       <c r="B42" t="n">
         <v>79084</v>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494035</v>
+        <v>493858</v>
       </c>
       <c r="R42" t="n">
-        <v>7035664</v>
+        <v>7035683</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5819,45 +5819,61 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129894465</v>
+        <v>129894433</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493746</v>
+        <v>493624</v>
       </c>
       <c r="R49" t="n">
-        <v>7035617</v>
+        <v>7035496</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5892,11 +5908,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gott om bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5905,6 +5916,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6023,61 +6039,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894433</v>
+        <v>129894465</v>
       </c>
       <c r="B51" t="n">
-        <v>58108</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493624</v>
+        <v>493746</v>
       </c>
       <c r="R51" t="n">
-        <v>7035496</v>
+        <v>7035617</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6112,6 +6112,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6120,11 +6125,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6354,32 +6354,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894426</v>
+        <v>129894474</v>
       </c>
       <c r="B54" t="n">
-        <v>80218</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493924</v>
+        <v>493922</v>
       </c>
       <c r="R54" t="n">
-        <v>7035590</v>
+        <v>7035751</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6456,32 +6456,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894474</v>
+        <v>129894426</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>80218</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493922</v>
+        <v>493924</v>
       </c>
       <c r="R55" t="n">
-        <v>7035751</v>
+        <v>7035590</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6558,7 +6558,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129894436</v>
+        <v>129894438</v>
       </c>
       <c r="B56" t="n">
         <v>98794</v>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493946</v>
+        <v>493981</v>
       </c>
       <c r="R56" t="n">
-        <v>7035738</v>
+        <v>7035656</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6682,7 +6682,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894438</v>
+        <v>129894436</v>
       </c>
       <c r="B57" t="n">
         <v>98794</v>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493981</v>
+        <v>493946</v>
       </c>
       <c r="R57" t="n">
-        <v>7035656</v>
+        <v>7035738</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,61 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894437</v>
+        <v>129894461</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493943</v>
+        <v>493611</v>
       </c>
       <c r="R2" t="n">
-        <v>7035674</v>
+        <v>7035450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,14 +759,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -799,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894461</v>
+        <v>129894447</v>
       </c>
       <c r="B3" t="n">
         <v>79095</v>
@@ -827,17 +805,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493611</v>
+        <v>493899</v>
       </c>
       <c r="R3" t="n">
-        <v>7035450</v>
+        <v>7035614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +863,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,8 +872,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -901,45 +916,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894447</v>
+        <v>129894437</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493899</v>
+        <v>493943</v>
       </c>
       <c r="R4" t="n">
-        <v>7035614</v>
+        <v>7035674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,26 +1023,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894425</v>
+        <v>129894441</v>
       </c>
       <c r="B46" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5503,50 +5503,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493632</v>
+        <v>493967</v>
       </c>
       <c r="R46" t="n">
-        <v>7035408</v>
+        <v>7035717</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5583,7 +5567,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
+          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5594,11 +5578,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5615,7 +5594,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894441</v>
+        <v>129894443</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5650,10 +5629,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493967</v>
+        <v>493892</v>
       </c>
       <c r="R47" t="n">
-        <v>7035717</v>
+        <v>7035776</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5690,7 +5669,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
+          <t>På en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5717,10 +5696,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894443</v>
+        <v>129894425</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5728,34 +5707,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493892</v>
+        <v>493632</v>
       </c>
       <c r="R48" t="n">
-        <v>7035776</v>
+        <v>7035408</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd.</t>
+          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5803,6 +5798,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,45 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894461</v>
+        <v>129894437</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493611</v>
+        <v>493943</v>
       </c>
       <c r="R2" t="n">
-        <v>7035450</v>
+        <v>7035674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,8 +775,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894447</v>
+        <v>129894461</v>
       </c>
       <c r="B3" t="n">
         <v>79095</v>
@@ -805,28 +827,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493899</v>
+        <v>493611</v>
       </c>
       <c r="R3" t="n">
-        <v>7035614</v>
+        <v>7035450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,34 +883,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,50 +901,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894437</v>
+        <v>129894447</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493943</v>
+        <v>493899</v>
       </c>
       <c r="R4" t="n">
-        <v>7035674</v>
+        <v>7035614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,6 +1003,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894429</v>
+        <v>129894480</v>
       </c>
       <c r="B15" t="n">
-        <v>97702</v>
+        <v>101020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,26 +2141,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2169,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494017</v>
+        <v>493987</v>
       </c>
       <c r="R15" t="n">
-        <v>7035651</v>
+        <v>7035633</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,6 +2209,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2580,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894480</v>
+        <v>129894429</v>
       </c>
       <c r="B19" t="n">
-        <v>101020</v>
+        <v>97702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,30 +2600,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493987</v>
+        <v>494017</v>
       </c>
       <c r="R19" t="n">
-        <v>7035633</v>
+        <v>7035651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,11 +2664,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3763,7 +3763,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894464</v>
+        <v>129894463</v>
       </c>
       <c r="B30" t="n">
         <v>79095</v>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493723</v>
+        <v>493634</v>
       </c>
       <c r="R30" t="n">
-        <v>7035578</v>
+        <v>7035511</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894432</v>
+        <v>129894428</v>
       </c>
       <c r="B31" t="n">
-        <v>58113</v>
+        <v>80229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3876,50 +3876,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493967</v>
+        <v>494023</v>
       </c>
       <c r="R31" t="n">
-        <v>7035617</v>
+        <v>7035675</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3956,7 +3947,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3965,12 +3956,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3988,52 +4000,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894428</v>
+        <v>129894450</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494023</v>
+        <v>493823</v>
       </c>
       <c r="R32" t="n">
-        <v>7035675</v>
+        <v>7035581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,7 +4075,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4079,34 +4084,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4123,7 +4102,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894450</v>
+        <v>129894464</v>
       </c>
       <c r="B33" t="n">
         <v>79095</v>
@@ -4158,10 +4137,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493823</v>
+        <v>493723</v>
       </c>
       <c r="R33" t="n">
-        <v>7035581</v>
+        <v>7035578</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4198,7 +4177,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4225,45 +4204,61 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894463</v>
+        <v>129894432</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>58113</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493634</v>
+        <v>493967</v>
       </c>
       <c r="R34" t="n">
-        <v>7035511</v>
+        <v>7035617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4300,7 +4295,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4311,6 +4306,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4633,10 +4633,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894467</v>
+        <v>129894431</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,34 +4644,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493793</v>
+        <v>493921</v>
       </c>
       <c r="R38" t="n">
-        <v>7035636</v>
+        <v>7035594</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,7 +4711,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4717,8 +4720,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4735,10 +4764,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894431</v>
+        <v>129894467</v>
       </c>
       <c r="B39" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4746,37 +4775,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493921</v>
+        <v>493793</v>
       </c>
       <c r="R39" t="n">
-        <v>7035594</v>
+        <v>7035636</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4813,7 +4839,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4822,34 +4848,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5492,10 +5492,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894441</v>
+        <v>129894425</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5503,34 +5503,50 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493967</v>
+        <v>493632</v>
       </c>
       <c r="R46" t="n">
-        <v>7035717</v>
+        <v>7035408</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5567,7 +5583,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
+          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5578,6 +5594,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5594,7 +5615,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894443</v>
+        <v>129894441</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5629,10 +5650,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493892</v>
+        <v>493967</v>
       </c>
       <c r="R47" t="n">
-        <v>7035776</v>
+        <v>7035717</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,7 +5690,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd.</t>
+          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5696,10 +5717,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894425</v>
+        <v>129894443</v>
       </c>
       <c r="B48" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5707,50 +5728,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493632</v>
+        <v>493892</v>
       </c>
       <c r="R48" t="n">
-        <v>7035408</v>
+        <v>7035776</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5787,7 +5792,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
+          <t>På en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5798,11 +5803,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129894437</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894461</v>
+        <v>129894447</v>
       </c>
       <c r="B3" t="n">
         <v>79095</v>
@@ -827,17 +827,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493611</v>
+        <v>493899</v>
       </c>
       <c r="R3" t="n">
-        <v>7035450</v>
+        <v>7035614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,8 +894,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -901,7 +938,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894447</v>
+        <v>129894461</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -929,28 +966,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493899</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7035614</v>
+        <v>7035450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,34 +1022,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129894449</v>
+        <v>129894440</v>
       </c>
       <c r="B7" t="n">
         <v>79095</v>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493828</v>
+        <v>493988</v>
       </c>
       <c r="R7" t="n">
-        <v>7035639</v>
+        <v>7035698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129894440</v>
+        <v>129894449</v>
       </c>
       <c r="B8" t="n">
         <v>79095</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493988</v>
+        <v>493828</v>
       </c>
       <c r="R8" t="n">
-        <v>7035698</v>
+        <v>7035639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1583,7 +1583,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129894444</v>
+        <v>129894442</v>
       </c>
       <c r="B10" t="n">
         <v>79095</v>
@@ -1611,28 +1611,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493977</v>
+        <v>493963</v>
       </c>
       <c r="R10" t="n">
-        <v>7035653</v>
+        <v>7035733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1658,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt och ymnigt på många granar i äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,34 +1667,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1722,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894442</v>
+        <v>129894444</v>
       </c>
       <c r="B11" t="n">
         <v>79095</v>
@@ -1750,17 +1713,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493963</v>
+        <v>493977</v>
       </c>
       <c r="R11" t="n">
-        <v>7035733</v>
+        <v>7035653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1771,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt och ymnigt på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,8 +1780,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1824,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894476</v>
+        <v>129894457</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494006</v>
+        <v>493307</v>
       </c>
       <c r="R12" t="n">
-        <v>7035657</v>
+        <v>7035159</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,7 +1926,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894457</v>
+        <v>129894476</v>
       </c>
       <c r="B13" t="n">
         <v>79095</v>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493307</v>
+        <v>494006</v>
       </c>
       <c r="R13" t="n">
-        <v>7035159</v>
+        <v>7035657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2031,7 @@
         <v>129894479</v>
       </c>
       <c r="B14" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,53 +2130,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894480</v>
+        <v>129894452</v>
       </c>
       <c r="B15" t="n">
-        <v>101020</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493987</v>
+        <v>493770</v>
       </c>
       <c r="R15" t="n">
-        <v>7035633</v>
+        <v>7035500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,7 +2205,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,14 +2214,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2348,7 +2334,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894452</v>
+        <v>129894446</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2376,17 +2362,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493770</v>
+        <v>493940</v>
       </c>
       <c r="R17" t="n">
-        <v>7035500</v>
+        <v>7035627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,8 +2429,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2450,45 +2473,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894446</v>
+        <v>129894480</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>101022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2496,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493940</v>
+        <v>493987</v>
       </c>
       <c r="R18" t="n">
-        <v>7035627</v>
+        <v>7035633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,7 +2556,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,26 +2572,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         <v>129894429</v>
       </c>
       <c r="B19" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894451</v>
+        <v>129894423</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>91641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2911,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493860</v>
+        <v>493910</v>
       </c>
       <c r="R22" t="n">
-        <v>7035559</v>
+        <v>7035709</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,7 +2982,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I en upplyft granlåga i en samling granlågor.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,8 +2991,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3002,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894423</v>
+        <v>129894451</v>
       </c>
       <c r="B23" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,41 +3046,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493910</v>
+        <v>493860</v>
       </c>
       <c r="R23" t="n">
-        <v>7035709</v>
+        <v>7035559</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,7 +3110,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i en samling granlågor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,34 +3119,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3137,7 +3137,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894475</v>
+        <v>129894453</v>
       </c>
       <c r="B24" t="n">
         <v>79095</v>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493953</v>
+        <v>493811</v>
       </c>
       <c r="R24" t="n">
-        <v>7035683</v>
+        <v>7035511</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894453</v>
+        <v>129894460</v>
       </c>
       <c r="B25" t="n">
         <v>79095</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493811</v>
+        <v>493489</v>
       </c>
       <c r="R25" t="n">
-        <v>7035511</v>
+        <v>7035303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129894460</v>
+        <v>129894475</v>
       </c>
       <c r="B26" t="n">
         <v>79095</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493489</v>
+        <v>493953</v>
       </c>
       <c r="R26" t="n">
-        <v>7035303</v>
+        <v>7035683</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,7 +3443,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129894455</v>
+        <v>129894456</v>
       </c>
       <c r="B27" t="n">
         <v>79095</v>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493715</v>
+        <v>493645</v>
       </c>
       <c r="R27" t="n">
-        <v>7035494</v>
+        <v>7035420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på flera granar.</t>
+          <t>Bland andra hänglavar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3545,7 +3545,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894456</v>
+        <v>129894455</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493645</v>
+        <v>493715</v>
       </c>
       <c r="R28" t="n">
-        <v>7035420</v>
+        <v>7035494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i granskog.</t>
+          <t>Rikligt och med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,7 +3650,7 @@
         <v>129894482</v>
       </c>
       <c r="B29" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,52 +3865,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894428</v>
+        <v>129894464</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494023</v>
+        <v>493723</v>
       </c>
       <c r="R31" t="n">
-        <v>7035675</v>
+        <v>7035578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3940,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3956,34 +3949,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4102,45 +4069,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894464</v>
+        <v>129894428</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493723</v>
+        <v>494023</v>
       </c>
       <c r="R33" t="n">
-        <v>7035578</v>
+        <v>7035675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,7 +4151,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,8 +4160,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4327,7 +4327,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894472</v>
+        <v>129894459</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493872</v>
+        <v>493464</v>
       </c>
       <c r="R35" t="n">
-        <v>7035742</v>
+        <v>7035297</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4429,7 +4429,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894459</v>
+        <v>129894472</v>
       </c>
       <c r="B36" t="n">
         <v>79095</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493464</v>
+        <v>493872</v>
       </c>
       <c r="R36" t="n">
-        <v>7035297</v>
+        <v>7035742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4633,10 +4633,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894431</v>
+        <v>129894467</v>
       </c>
       <c r="B38" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,37 +4644,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493921</v>
+        <v>493793</v>
       </c>
       <c r="R38" t="n">
-        <v>7035594</v>
+        <v>7035636</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4711,7 +4708,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4720,34 +4717,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4764,10 +4735,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894467</v>
+        <v>129894431</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4775,34 +4746,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493793</v>
+        <v>493921</v>
       </c>
       <c r="R39" t="n">
-        <v>7035636</v>
+        <v>7035594</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4839,7 +4813,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,8 +4822,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4869,7 +4869,7 @@
         <v>129894481</v>
       </c>
       <c r="B40" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894445</v>
+        <v>129894469</v>
       </c>
       <c r="B41" t="n">
         <v>79095</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493904</v>
+        <v>493858</v>
       </c>
       <c r="R41" t="n">
-        <v>7035660</v>
+        <v>7035683</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,7 +5084,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894448</v>
+        <v>129894477</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493853</v>
+        <v>494035</v>
       </c>
       <c r="R42" t="n">
-        <v>7035633</v>
+        <v>7035664</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på gran.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,7 +5186,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894469</v>
+        <v>129894445</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493858</v>
+        <v>493904</v>
       </c>
       <c r="R43" t="n">
-        <v>7035683</v>
+        <v>7035660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,7 +5288,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894477</v>
+        <v>129894448</v>
       </c>
       <c r="B44" t="n">
         <v>79095</v>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494035</v>
+        <v>493853</v>
       </c>
       <c r="R44" t="n">
-        <v>7035664</v>
+        <v>7035633</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>Hyfsat rikligt på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,10 +5492,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894425</v>
+        <v>129894443</v>
       </c>
       <c r="B46" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5503,50 +5503,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493632</v>
+        <v>493892</v>
       </c>
       <c r="R46" t="n">
-        <v>7035408</v>
+        <v>7035776</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5583,7 +5567,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
+          <t>På en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5594,11 +5578,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5717,10 +5696,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894443</v>
+        <v>129894425</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5728,34 +5707,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493892</v>
+        <v>493632</v>
       </c>
       <c r="R48" t="n">
-        <v>7035776</v>
+        <v>7035408</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd.</t>
+          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5803,6 +5798,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129894465</v>
+        <v>129894473</v>
       </c>
       <c r="B49" t="n">
         <v>79095</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493746</v>
+        <v>493901</v>
       </c>
       <c r="R49" t="n">
-        <v>7035617</v>
+        <v>7035798</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gott om bålar på flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894473</v>
+        <v>129894465</v>
       </c>
       <c r="B50" t="n">
         <v>79095</v>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493901</v>
+        <v>493746</v>
       </c>
       <c r="R50" t="n">
-        <v>7035798</v>
+        <v>7035617</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Gott om bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6023,10 +6023,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894433</v>
+        <v>129894483</v>
       </c>
       <c r="B51" t="n">
-        <v>58113</v>
+        <v>101022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6034,50 +6034,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493624</v>
+        <v>493945</v>
       </c>
       <c r="R51" t="n">
-        <v>7035496</v>
+        <v>7035601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6118,6 +6110,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6141,10 +6134,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894483</v>
+        <v>129894433</v>
       </c>
       <c r="B52" t="n">
-        <v>101020</v>
+        <v>58113</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6152,42 +6145,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493945</v>
+        <v>493624</v>
       </c>
       <c r="R52" t="n">
-        <v>7035601</v>
+        <v>7035496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6228,7 +6229,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6354,45 +6354,61 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894426</v>
+        <v>129894438</v>
       </c>
       <c r="B54" t="n">
-        <v>80229</v>
+        <v>98833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493924</v>
+        <v>493981</v>
       </c>
       <c r="R54" t="n">
-        <v>7035590</v>
+        <v>7035656</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6445,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6438,8 +6454,14 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6456,45 +6478,61 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894474</v>
+        <v>129894436</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493922</v>
+        <v>493946</v>
       </c>
       <c r="R55" t="n">
-        <v>7035751</v>
+        <v>7035738</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6531,7 +6569,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6540,8 +6578,14 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6558,61 +6602,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129894438</v>
+        <v>129894474</v>
       </c>
       <c r="B56" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493981</v>
+        <v>493922</v>
       </c>
       <c r="R56" t="n">
-        <v>7035656</v>
+        <v>7035751</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6649,7 +6677,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,14 +6686,8 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6682,61 +6704,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894436</v>
+        <v>129894426</v>
       </c>
       <c r="B57" t="n">
-        <v>98831</v>
+        <v>80229</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493946</v>
+        <v>493924</v>
       </c>
       <c r="R57" t="n">
-        <v>7035738</v>
+        <v>7035590</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6773,7 +6779,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6782,14 +6788,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129894437</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129894447</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>129894461</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129894458</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>129894470</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129894440</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129894449</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>129894427</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>129894442</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>129894444</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,32 +1824,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894457</v>
+        <v>129894479</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>101109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493307</v>
+        <v>493970</v>
       </c>
       <c r="R12" t="n">
-        <v>7035159</v>
+        <v>7035615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894476</v>
+        <v>129894457</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494006</v>
+        <v>493307</v>
       </c>
       <c r="R13" t="n">
-        <v>7035657</v>
+        <v>7035159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894479</v>
+        <v>129894476</v>
       </c>
       <c r="B14" t="n">
-        <v>101022</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493970</v>
+        <v>494006</v>
       </c>
       <c r="R14" t="n">
-        <v>7035615</v>
+        <v>7035657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,45 +2130,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894452</v>
+        <v>129894480</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>101109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493770</v>
+        <v>493987</v>
       </c>
       <c r="R15" t="n">
-        <v>7035500</v>
+        <v>7035633</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,7 +2213,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,8 +2222,14 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2232,45 +2246,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129894439</v>
+        <v>129894429</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493917</v>
+        <v>494017</v>
       </c>
       <c r="R16" t="n">
-        <v>7035788</v>
+        <v>7035651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,19 +2323,20 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2334,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894446</v>
+        <v>129894439</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,28 +2381,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493940</v>
+        <v>493917</v>
       </c>
       <c r="R17" t="n">
-        <v>7035627</v>
+        <v>7035788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,7 +2428,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,34 +2437,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2473,53 +2455,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894480</v>
+        <v>129894452</v>
       </c>
       <c r="B18" t="n">
-        <v>101022</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493987</v>
+        <v>493770</v>
       </c>
       <c r="R18" t="n">
-        <v>7035633</v>
+        <v>7035500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2530,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,14 +2539,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2589,38 +2557,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894429</v>
+        <v>129894446</v>
       </c>
       <c r="B19" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2628,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494017</v>
+        <v>493940</v>
       </c>
       <c r="R19" t="n">
-        <v>7035651</v>
+        <v>7035627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,6 +2641,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2679,6 +2659,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>129894462</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>129894454</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894423</v>
+        <v>129894451</v>
       </c>
       <c r="B22" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,41 +2911,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493910</v>
+        <v>493860</v>
       </c>
       <c r="R22" t="n">
-        <v>7035709</v>
+        <v>7035559</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2982,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i en samling granlågor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2991,34 +2984,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3035,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894451</v>
+        <v>129894423</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>91728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,34 +3013,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493860</v>
+        <v>493910</v>
       </c>
       <c r="R23" t="n">
-        <v>7035559</v>
+        <v>7035709</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,7 +3084,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I en upplyft granlåga i en samling granlågor.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,8 +3093,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3140,7 +3140,7 @@
         <v>129894453</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129894460</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129894475</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>129894456</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129894455</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>129894482</v>
       </c>
       <c r="B29" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,45 +3763,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894463</v>
+        <v>129894428</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>80314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493634</v>
+        <v>494023</v>
       </c>
       <c r="R30" t="n">
-        <v>7035511</v>
+        <v>7035675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,7 +3845,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,8 +3854,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3865,10 +3898,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894464</v>
+        <v>129894463</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3900,10 +3933,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493723</v>
+        <v>493634</v>
       </c>
       <c r="R31" t="n">
-        <v>7035578</v>
+        <v>7035511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3973,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3967,10 +4000,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894450</v>
+        <v>129894464</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4002,10 +4035,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493823</v>
+        <v>493723</v>
       </c>
       <c r="R32" t="n">
-        <v>7035581</v>
+        <v>7035578</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,7 +4075,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4069,52 +4102,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894428</v>
+        <v>129894450</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494023</v>
+        <v>493823</v>
       </c>
       <c r="R33" t="n">
-        <v>7035675</v>
+        <v>7035581</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4151,7 +4177,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,34 +4186,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4207,7 +4207,7 @@
         <v>129894432</v>
       </c>
       <c r="B34" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>129894459</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>129894472</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>129894471</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>129894467</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4735,37 +4735,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894431</v>
+        <v>129894481</v>
       </c>
       <c r="B39" t="n">
-        <v>80200</v>
+        <v>101109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4773,10 +4778,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493921</v>
+        <v>493990</v>
       </c>
       <c r="R39" t="n">
-        <v>7035594</v>
+        <v>7035652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4813,7 +4818,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,26 +4834,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4866,42 +4851,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894481</v>
+        <v>129894431</v>
       </c>
       <c r="B40" t="n">
-        <v>101022</v>
+        <v>80285</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4909,10 +4889,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493990</v>
+        <v>493921</v>
       </c>
       <c r="R40" t="n">
-        <v>7035652</v>
+        <v>7035594</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4949,7 +4929,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,6 +4945,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
         <v>129894469</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>129894477</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894445</v>
+        <v>129894448</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493904</v>
+        <v>493853</v>
       </c>
       <c r="R43" t="n">
-        <v>7035660</v>
+        <v>7035633</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>Hyfsat rikligt på gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,10 +5288,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894448</v>
+        <v>129894468</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493853</v>
+        <v>493808</v>
       </c>
       <c r="R44" t="n">
-        <v>7035633</v>
+        <v>7035662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på gran.</t>
+          <t>På flera granar och på bark av tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894468</v>
+        <v>129894445</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493808</v>
+        <v>493904</v>
       </c>
       <c r="R45" t="n">
-        <v>7035662</v>
+        <v>7035660</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På flera granar och på bark av tall.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5495,7 +5495,7 @@
         <v>129894443</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5594,10 +5594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894441</v>
+        <v>129894425</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>57985</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,34 +5605,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493967</v>
+        <v>493632</v>
       </c>
       <c r="R47" t="n">
-        <v>7035717</v>
+        <v>7035408</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,7 +5685,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
+          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5680,6 +5696,11 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5696,10 +5717,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894425</v>
+        <v>129894441</v>
       </c>
       <c r="B48" t="n">
-        <v>57900</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5707,50 +5728,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493632</v>
+        <v>493967</v>
       </c>
       <c r="R48" t="n">
-        <v>7035408</v>
+        <v>7035717</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5787,7 +5792,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
+          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5798,11 +5803,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5822,7 +5822,7 @@
         <v>129894473</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5921,45 +5921,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894465</v>
+        <v>129894483</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>101109</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493746</v>
+        <v>493945</v>
       </c>
       <c r="R50" t="n">
-        <v>7035617</v>
+        <v>7035601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5994,19 +6002,20 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Gott om bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6023,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894483</v>
+        <v>129894433</v>
       </c>
       <c r="B51" t="n">
-        <v>101022</v>
+        <v>58198</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6034,42 +6043,50 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493945</v>
+        <v>493624</v>
       </c>
       <c r="R51" t="n">
-        <v>7035601</v>
+        <v>7035496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6110,7 +6127,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6134,61 +6150,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894433</v>
+        <v>129894465</v>
       </c>
       <c r="B52" t="n">
-        <v>58113</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493624</v>
+        <v>493746</v>
       </c>
       <c r="R52" t="n">
-        <v>7035496</v>
+        <v>7035617</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6223,6 +6223,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gott om bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6231,11 +6236,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6255,7 +6255,7 @@
         <v>129894466</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,61 +6354,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894438</v>
+        <v>129894426</v>
       </c>
       <c r="B54" t="n">
-        <v>98833</v>
+        <v>80314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493981</v>
+        <v>493924</v>
       </c>
       <c r="R54" t="n">
-        <v>7035656</v>
+        <v>7035590</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,7 +6429,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6454,14 +6438,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6478,61 +6456,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894436</v>
+        <v>129894474</v>
       </c>
       <c r="B55" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493946</v>
+        <v>493922</v>
       </c>
       <c r="R55" t="n">
-        <v>7035738</v>
+        <v>7035751</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6569,7 +6531,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6578,14 +6540,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6602,45 +6558,61 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129894474</v>
+        <v>129894438</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493922</v>
+        <v>493981</v>
       </c>
       <c r="R56" t="n">
-        <v>7035751</v>
+        <v>7035656</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6677,7 +6649,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6686,8 +6658,14 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6704,45 +6682,61 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894426</v>
+        <v>129894436</v>
       </c>
       <c r="B57" t="n">
-        <v>80229</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493924</v>
+        <v>493946</v>
       </c>
       <c r="R57" t="n">
-        <v>7035590</v>
+        <v>7035738</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6779,7 +6773,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6788,8 +6782,14 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -1824,32 +1824,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894479</v>
+        <v>129894457</v>
       </c>
       <c r="B12" t="n">
-        <v>101109</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493970</v>
+        <v>493307</v>
       </c>
       <c r="R12" t="n">
-        <v>7035615</v>
+        <v>7035159</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,7 +1926,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894457</v>
+        <v>129894476</v>
       </c>
       <c r="B13" t="n">
         <v>79180</v>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493307</v>
+        <v>494006</v>
       </c>
       <c r="R13" t="n">
-        <v>7035159</v>
+        <v>7035657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894476</v>
+        <v>129894479</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>101109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494006</v>
+        <v>493970</v>
       </c>
       <c r="R14" t="n">
-        <v>7035657</v>
+        <v>7035615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894480</v>
+        <v>129894429</v>
       </c>
       <c r="B15" t="n">
-        <v>101109</v>
+        <v>97791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,30 +2141,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2173,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493987</v>
+        <v>494017</v>
       </c>
       <c r="R15" t="n">
-        <v>7035633</v>
+        <v>7035651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,11 +2205,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129894429</v>
+        <v>129894480</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>101109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,26 +2248,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494017</v>
+        <v>493987</v>
       </c>
       <c r="R16" t="n">
-        <v>7035651</v>
+        <v>7035633</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,6 +2316,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129894437</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129894447</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>129894461</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>129894458</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>129894470</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129894440</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129894449</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>129894427</v>
       </c>
       <c r="B9" t="n">
-        <v>80314</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>129894442</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>129894444</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>129894457</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>129894476</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>129894479</v>
       </c>
       <c r="B14" t="n">
-        <v>101109</v>
+        <v>101022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,49 +2130,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894429</v>
+        <v>129894452</v>
       </c>
       <c r="B15" t="n">
-        <v>97791</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494017</v>
+        <v>493770</v>
       </c>
       <c r="R15" t="n">
-        <v>7035651</v>
+        <v>7035500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,20 +2203,19 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2237,53 +2232,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129894480</v>
+        <v>129894439</v>
       </c>
       <c r="B16" t="n">
-        <v>101109</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493987</v>
+        <v>493917</v>
       </c>
       <c r="R16" t="n">
-        <v>7035633</v>
+        <v>7035788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,7 +2307,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,14 +2316,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2353,10 +2334,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894439</v>
+        <v>129894446</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,17 +2362,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493917</v>
+        <v>493940</v>
       </c>
       <c r="R17" t="n">
-        <v>7035788</v>
+        <v>7035627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,7 +2420,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,8 +2429,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2455,45 +2473,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894452</v>
+        <v>129894480</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>101022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493770</v>
+        <v>493987</v>
       </c>
       <c r="R18" t="n">
-        <v>7035500</v>
+        <v>7035633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,7 +2556,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,8 +2565,14 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2557,45 +2589,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894446</v>
+        <v>129894429</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>97704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2603,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493940</v>
+        <v>494017</v>
       </c>
       <c r="R19" t="n">
-        <v>7035627</v>
+        <v>7035651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,11 +2666,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2659,26 +2679,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>129894462</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>129894454</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894451</v>
+        <v>129894423</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>91641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2911,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493860</v>
+        <v>493910</v>
       </c>
       <c r="R22" t="n">
-        <v>7035559</v>
+        <v>7035709</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,7 +2982,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I en upplyft granlåga i en samling granlågor.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,8 +2991,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3002,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894423</v>
+        <v>129894451</v>
       </c>
       <c r="B23" t="n">
-        <v>91728</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,41 +3046,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493910</v>
+        <v>493860</v>
       </c>
       <c r="R23" t="n">
-        <v>7035709</v>
+        <v>7035559</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3084,7 +3110,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i en samling granlågor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,34 +3119,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3140,7 +3140,7 @@
         <v>129894453</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129894460</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>129894475</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>129894456</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129894455</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>129894482</v>
       </c>
       <c r="B29" t="n">
-        <v>101109</v>
+        <v>101022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,52 +3763,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894428</v>
+        <v>129894463</v>
       </c>
       <c r="B30" t="n">
-        <v>80314</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494023</v>
+        <v>493634</v>
       </c>
       <c r="R30" t="n">
-        <v>7035675</v>
+        <v>7035511</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3838,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,34 +3847,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3898,10 +3865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894463</v>
+        <v>129894464</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3933,10 +3900,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493634</v>
+        <v>493723</v>
       </c>
       <c r="R31" t="n">
-        <v>7035511</v>
+        <v>7035578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3973,7 +3940,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,10 +3967,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894464</v>
+        <v>129894450</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,10 +4002,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493723</v>
+        <v>493823</v>
       </c>
       <c r="R32" t="n">
-        <v>7035578</v>
+        <v>7035581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4075,7 +4042,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4102,45 +4069,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894450</v>
+        <v>129894428</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493823</v>
+        <v>494023</v>
       </c>
       <c r="R33" t="n">
-        <v>7035581</v>
+        <v>7035675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,7 +4151,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,8 +4160,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4207,7 +4207,7 @@
         <v>129894432</v>
       </c>
       <c r="B34" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>129894459</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>129894472</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>129894471</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>129894467</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4735,42 +4735,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894481</v>
+        <v>129894431</v>
       </c>
       <c r="B39" t="n">
-        <v>101109</v>
+        <v>80200</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4778,10 +4773,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493990</v>
+        <v>493921</v>
       </c>
       <c r="R39" t="n">
-        <v>7035652</v>
+        <v>7035594</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4818,7 +4813,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,6 +4829,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4851,37 +4866,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894431</v>
+        <v>129894481</v>
       </c>
       <c r="B40" t="n">
-        <v>80285</v>
+        <v>101022</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4889,10 +4909,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493921</v>
+        <v>493990</v>
       </c>
       <c r="R40" t="n">
-        <v>7035594</v>
+        <v>7035652</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4929,7 +4949,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4945,26 +4965,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
         <v>129894469</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>129894477</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894448</v>
+        <v>129894445</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493853</v>
+        <v>493904</v>
       </c>
       <c r="R43" t="n">
-        <v>7035633</v>
+        <v>7035660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på gran.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,10 +5288,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894468</v>
+        <v>129894448</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493808</v>
+        <v>493853</v>
       </c>
       <c r="R44" t="n">
-        <v>7035662</v>
+        <v>7035633</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På flera granar och på bark av tall.</t>
+          <t>Hyfsat rikligt på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894445</v>
+        <v>129894468</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493904</v>
+        <v>493808</v>
       </c>
       <c r="R45" t="n">
-        <v>7035660</v>
+        <v>7035662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>På flera granar och på bark av tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5495,7 +5495,7 @@
         <v>129894443</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5594,10 +5594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894425</v>
+        <v>129894441</v>
       </c>
       <c r="B47" t="n">
-        <v>57985</v>
+        <v>79095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5605,50 +5605,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493632</v>
+        <v>493967</v>
       </c>
       <c r="R47" t="n">
-        <v>7035408</v>
+        <v>7035717</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5685,7 +5669,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
+          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5696,11 +5680,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5717,10 +5696,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894441</v>
+        <v>129894425</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>57900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5728,34 +5707,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493967</v>
+        <v>493632</v>
       </c>
       <c r="R48" t="n">
-        <v>7035717</v>
+        <v>7035408</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5792,7 +5787,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
+          <t>Synobservation av minst 2 individer, födosökande med lockläte i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5803,6 +5798,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5822,7 +5822,7 @@
         <v>129894473</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5921,53 +5921,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894483</v>
+        <v>129894465</v>
       </c>
       <c r="B50" t="n">
-        <v>101109</v>
+        <v>79095</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493945</v>
+        <v>493746</v>
       </c>
       <c r="R50" t="n">
-        <v>7035601</v>
+        <v>7035617</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6002,20 +5994,19 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gott om bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6032,10 +6023,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894433</v>
+        <v>129894483</v>
       </c>
       <c r="B51" t="n">
-        <v>58198</v>
+        <v>101022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,50 +6034,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493624</v>
+        <v>493945</v>
       </c>
       <c r="R51" t="n">
-        <v>7035496</v>
+        <v>7035601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6127,6 +6110,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6150,45 +6134,61 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894465</v>
+        <v>129894433</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>58113</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493746</v>
+        <v>493624</v>
       </c>
       <c r="R52" t="n">
-        <v>7035617</v>
+        <v>7035496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6223,11 +6223,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gott om bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6236,6 +6231,11 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6255,7 +6255,7 @@
         <v>129894466</v>
       </c>
       <c r="B53" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,45 +6354,61 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894426</v>
+        <v>129894438</v>
       </c>
       <c r="B54" t="n">
-        <v>80314</v>
+        <v>98833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493924</v>
+        <v>493981</v>
       </c>
       <c r="R54" t="n">
-        <v>7035590</v>
+        <v>7035656</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6445,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På barken av en levande sälg.</t>
+          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6438,8 +6454,14 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6456,45 +6478,61 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894474</v>
+        <v>129894436</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>98833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493922</v>
+        <v>493946</v>
       </c>
       <c r="R55" t="n">
-        <v>7035751</v>
+        <v>7035738</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6531,7 +6569,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6540,8 +6578,14 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6558,61 +6602,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129894438</v>
+        <v>129894474</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493981</v>
+        <v>493922</v>
       </c>
       <c r="R56" t="n">
-        <v>7035656</v>
+        <v>7035751</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6649,7 +6677,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,14 +6686,8 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6682,61 +6704,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894436</v>
+        <v>129894426</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>80229</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493946</v>
+        <v>493924</v>
       </c>
       <c r="R57" t="n">
-        <v>7035738</v>
+        <v>7035590</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6773,7 +6779,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6782,14 +6788,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -675,50 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894437</v>
+        <v>129894423</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493943</v>
+        <v>493910</v>
       </c>
       <c r="R2" t="n">
-        <v>7035674</v>
+        <v>7035709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>I en upplyft granlåga i en samling granlågor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +773,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,14 +810,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894447</v>
+        <v>129894439</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,28 +838,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493899</v>
+        <v>493917</v>
       </c>
       <c r="R3" t="n">
-        <v>7035614</v>
+        <v>7035788</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,34 +894,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -938,14 +912,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894461</v>
+        <v>129894440</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -973,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493988</v>
       </c>
       <c r="R4" t="n">
-        <v>7035450</v>
+        <v>7035698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,14 +1014,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129894458</v>
+        <v>129894441</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1075,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493261</v>
+        <v>493967</v>
       </c>
       <c r="R5" t="n">
-        <v>7035114</v>
+        <v>7035717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1089,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,14 +1116,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894470</v>
+        <v>129894442</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1177,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493963</v>
       </c>
       <c r="R6" t="n">
-        <v>7035688</v>
+        <v>7035733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1191,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,14 +1218,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129894440</v>
+        <v>129894443</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1279,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493988</v>
+        <v>493892</v>
       </c>
       <c r="R7" t="n">
-        <v>7035698</v>
+        <v>7035776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1293,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,14 +1320,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129894449</v>
+        <v>129894444</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1374,17 +1348,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493828</v>
+        <v>493977</v>
       </c>
       <c r="R8" t="n">
-        <v>7035639</v>
+        <v>7035653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1406,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt och ymnigt på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,8 +1415,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1448,52 +1459,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129894427</v>
+        <v>129894445</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493703</v>
+        <v>493904</v>
       </c>
       <c r="R9" t="n">
-        <v>7035573</v>
+        <v>7035660</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1534,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,34 +1543,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1583,14 +1561,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129894442</v>
+        <v>129894446</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1611,17 +1589,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493963</v>
+        <v>493940</v>
       </c>
       <c r="R10" t="n">
-        <v>7035733</v>
+        <v>7035627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1647,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,8 +1656,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1685,14 +1700,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894444</v>
+        <v>129894447</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1731,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493977</v>
+        <v>493899</v>
       </c>
       <c r="R11" t="n">
-        <v>7035653</v>
+        <v>7035614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1786,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt och ymnigt på många granar i äldre granskog.</t>
+          <t>Rikligt med långväxta bålar på många granar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,14 +1839,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894457</v>
+        <v>129894448</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1859,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493307</v>
+        <v>493853</v>
       </c>
       <c r="R12" t="n">
-        <v>7035159</v>
+        <v>7035633</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1914,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Hyfsat rikligt på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,14 +1941,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894476</v>
+        <v>129894449</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1961,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494006</v>
+        <v>493828</v>
       </c>
       <c r="R13" t="n">
-        <v>7035657</v>
+        <v>7035639</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2016,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2043,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894479</v>
+        <v>129894450</v>
       </c>
       <c r="B14" t="n">
-        <v>101022</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493970</v>
+        <v>493823</v>
       </c>
       <c r="R14" t="n">
-        <v>7035615</v>
+        <v>7035581</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2118,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,14 +2145,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894452</v>
+        <v>129894451</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2165,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493770</v>
+        <v>493860</v>
       </c>
       <c r="R15" t="n">
-        <v>7035500</v>
+        <v>7035559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,14 +2247,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129894439</v>
+        <v>129894452</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2267,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493917</v>
+        <v>493770</v>
       </c>
       <c r="R16" t="n">
-        <v>7035788</v>
+        <v>7035500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,7 +2322,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,14 +2349,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894446</v>
+        <v>129894453</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2362,28 +2377,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493940</v>
+        <v>493811</v>
       </c>
       <c r="R17" t="n">
-        <v>7035627</v>
+        <v>7035511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,34 +2433,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2473,53 +2451,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894480</v>
+        <v>129894454</v>
       </c>
       <c r="B18" t="n">
-        <v>101022</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493987</v>
+        <v>493694</v>
       </c>
       <c r="R18" t="n">
-        <v>7035633</v>
+        <v>7035412</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2526,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,14 +2535,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2589,49 +2553,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894429</v>
+        <v>129894455</v>
       </c>
       <c r="B19" t="n">
-        <v>97704</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494017</v>
+        <v>493715</v>
       </c>
       <c r="R19" t="n">
-        <v>7035651</v>
+        <v>7035494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,20 +2626,19 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt och med långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2696,14 +2655,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894462</v>
+        <v>129894456</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2731,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493596</v>
+        <v>493645</v>
       </c>
       <c r="R20" t="n">
-        <v>7035472</v>
+        <v>7035420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2730,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Bland andra hänglavar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,14 +2757,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894454</v>
+        <v>129894457</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2833,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493694</v>
+        <v>493307</v>
       </c>
       <c r="R21" t="n">
-        <v>7035412</v>
+        <v>7035159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2832,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,52 +2859,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894423</v>
+        <v>129894458</v>
       </c>
       <c r="B22" t="n">
-        <v>91641</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493910</v>
+        <v>493261</v>
       </c>
       <c r="R22" t="n">
-        <v>7035709</v>
+        <v>7035114</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2982,7 +2934,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga i en samling granlågor.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2991,34 +2943,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3035,14 +2961,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894451</v>
+        <v>129894459</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3070,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493860</v>
+        <v>493464</v>
       </c>
       <c r="R23" t="n">
-        <v>7035559</v>
+        <v>7035297</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,7 +3036,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,14 +3063,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894453</v>
+        <v>129894460</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3172,10 +3098,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493811</v>
+        <v>493489</v>
       </c>
       <c r="R24" t="n">
-        <v>7035511</v>
+        <v>7035303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,7 +3138,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,14 +3165,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894460</v>
+        <v>129894461</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3274,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493489</v>
+        <v>493611</v>
       </c>
       <c r="R25" t="n">
-        <v>7035303</v>
+        <v>7035450</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3314,7 +3240,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,14 +3267,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129894475</v>
+        <v>129894462</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3376,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493953</v>
+        <v>493596</v>
       </c>
       <c r="R26" t="n">
-        <v>7035683</v>
+        <v>7035472</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,7 +3342,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,14 +3369,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129894456</v>
+        <v>129894463</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3478,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493645</v>
+        <v>493634</v>
       </c>
       <c r="R27" t="n">
-        <v>7035420</v>
+        <v>7035511</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3518,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på gran i granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3545,14 +3471,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894455</v>
+        <v>129894464</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3580,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493715</v>
+        <v>493723</v>
       </c>
       <c r="R28" t="n">
-        <v>7035494</v>
+        <v>7035578</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3620,7 +3546,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt och med långväxta bålar på flera granar.</t>
+          <t>I riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,53 +3573,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894482</v>
+        <v>129894465</v>
       </c>
       <c r="B29" t="n">
-        <v>101022</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493912</v>
+        <v>493746</v>
       </c>
       <c r="R29" t="n">
-        <v>7035578</v>
+        <v>7035617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3730,7 +3648,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I ett relativt örtrikt stråk i granskog.</t>
+          <t>Gott om bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,14 +3657,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3763,14 +3675,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894463</v>
+        <v>129894466</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3798,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493634</v>
+        <v>493768</v>
       </c>
       <c r="R30" t="n">
-        <v>7035511</v>
+        <v>7035624</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3838,7 +3750,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3865,14 +3777,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894464</v>
+        <v>129894467</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3900,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493723</v>
+        <v>493793</v>
       </c>
       <c r="R31" t="n">
-        <v>7035578</v>
+        <v>7035636</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3852,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I riklig mängd på en gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3967,14 +3879,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894450</v>
+        <v>129894468</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4002,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493823</v>
+        <v>493808</v>
       </c>
       <c r="R32" t="n">
-        <v>7035581</v>
+        <v>7035662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,7 +3954,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på flera granar, både levande och döda träd.</t>
+          <t>På flera granar och på bark av tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4069,52 +3981,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894428</v>
+        <v>129894469</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494023</v>
+        <v>493858</v>
       </c>
       <c r="R33" t="n">
-        <v>7035675</v>
+        <v>7035683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4151,7 +4056,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På barken av en levande gammal sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,34 +4065,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4204,61 +4083,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894432</v>
+        <v>129894470</v>
       </c>
       <c r="B34" t="n">
-        <v>58113</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493967</v>
+        <v>493838</v>
       </c>
       <c r="R34" t="n">
-        <v>7035617</v>
+        <v>7035688</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4295,7 +4158,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4306,11 +4169,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4327,14 +4185,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894459</v>
+        <v>129894471</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4362,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493464</v>
+        <v>493842</v>
       </c>
       <c r="R35" t="n">
-        <v>7035297</v>
+        <v>7035721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,7 +4260,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,11 +4290,11 @@
         <v>129894472</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4531,14 +4389,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894471</v>
+        <v>129894473</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4566,10 +4424,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493842</v>
+        <v>493901</v>
       </c>
       <c r="R37" t="n">
-        <v>7035721</v>
+        <v>7035798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4633,14 +4491,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894467</v>
+        <v>129894474</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4668,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493793</v>
+        <v>493922</v>
       </c>
       <c r="R38" t="n">
-        <v>7035636</v>
+        <v>7035751</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4735,48 +4593,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894431</v>
+        <v>129894475</v>
       </c>
       <c r="B39" t="n">
-        <v>80200</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493921</v>
+        <v>493953</v>
       </c>
       <c r="R39" t="n">
-        <v>7035594</v>
+        <v>7035683</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4813,7 +4668,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på barken av en levande sälg.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4822,34 +4677,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4866,53 +4695,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894481</v>
+        <v>129894476</v>
       </c>
       <c r="B40" t="n">
-        <v>101022</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493990</v>
+        <v>494006</v>
       </c>
       <c r="R40" t="n">
-        <v>7035652</v>
+        <v>7035657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4949,7 +4770,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4958,14 +4779,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4982,14 +4797,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894469</v>
+        <v>129894477</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5017,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493858</v>
+        <v>494035</v>
       </c>
       <c r="R41" t="n">
-        <v>7035683</v>
+        <v>7035664</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5057,7 +4872,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Relativt rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,10 +4899,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894477</v>
+        <v>129894431</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5095,34 +4910,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494035</v>
+        <v>493921</v>
       </c>
       <c r="R42" t="n">
-        <v>7035664</v>
+        <v>7035594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,7 +4977,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>Enstaka bålar på barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5168,8 +4986,34 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5186,32 +5030,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894445</v>
+        <v>129894426</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5221,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493904</v>
+        <v>493924</v>
       </c>
       <c r="R43" t="n">
-        <v>7035660</v>
+        <v>7035590</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5105,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar i äldre flerskiktad granskog.</t>
+          <t>På barken av en levande sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,45 +5132,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894448</v>
+        <v>129894427</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493853</v>
+        <v>493703</v>
       </c>
       <c r="R44" t="n">
-        <v>7035633</v>
+        <v>7035573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,7 +5214,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt på gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,8 +5223,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5390,45 +5267,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894468</v>
+        <v>129894428</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493808</v>
+        <v>494023</v>
       </c>
       <c r="R45" t="n">
-        <v>7035662</v>
+        <v>7035675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,7 +5349,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På flera granar och på bark av tall.</t>
+          <t>På barken av en levande gammal sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5474,8 +5358,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5492,45 +5402,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894443</v>
+        <v>129894432</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>58327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493892</v>
+        <v>493967</v>
       </c>
       <c r="R46" t="n">
-        <v>7035776</v>
+        <v>7035617</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5567,7 +5493,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd.</t>
+          <t>1 individ med lockläte, i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5578,6 +5504,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5594,45 +5525,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894441</v>
+        <v>129894433</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>58327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493967</v>
+        <v>493624</v>
       </c>
       <c r="R47" t="n">
-        <v>7035717</v>
+        <v>7035496</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5667,11 +5614,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med bålar på en stående död gran med full längd och över 30 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5680,6 +5622,11 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5699,7 +5646,7 @@
         <v>129894425</v>
       </c>
       <c r="B48" t="n">
-        <v>57900</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5819,45 +5766,61 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129894473</v>
+        <v>129894436</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493901</v>
+        <v>493946</v>
       </c>
       <c r="R49" t="n">
-        <v>7035798</v>
+        <v>7035738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5894,7 +5857,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5903,8 +5866,14 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5921,45 +5890,61 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894465</v>
+        <v>129894437</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493746</v>
+        <v>493943</v>
       </c>
       <c r="R50" t="n">
-        <v>7035617</v>
+        <v>7035674</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,7 +5981,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gott om bålar på flera granar.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 0,5 m2 yta i äldre garnlavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6005,8 +5990,14 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6023,36 +6014,44 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894483</v>
+        <v>129894438</v>
       </c>
       <c r="B51" t="n">
-        <v>101022</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6066,10 +6065,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493945</v>
+        <v>493981</v>
       </c>
       <c r="R51" t="n">
-        <v>7035601</v>
+        <v>7035656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6102,6 +6101,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6134,10 +6138,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894433</v>
+        <v>129894429</v>
       </c>
       <c r="B52" t="n">
-        <v>58113</v>
+        <v>97983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6145,50 +6149,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493624</v>
+        <v>494017</v>
       </c>
       <c r="R52" t="n">
-        <v>7035496</v>
+        <v>7035651</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6229,6 +6221,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6252,32 +6245,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129894466</v>
+        <v>129894479</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>101325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6287,10 +6280,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493768</v>
+        <v>493970</v>
       </c>
       <c r="R53" t="n">
-        <v>7035624</v>
+        <v>7035615</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6327,7 +6320,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6354,44 +6347,36 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129894438</v>
+        <v>129894480</v>
       </c>
       <c r="B54" t="n">
-        <v>98833</v>
+        <v>101325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6405,10 +6390,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493981</v>
+        <v>493987</v>
       </c>
       <c r="R54" t="n">
-        <v>7035656</v>
+        <v>7035633</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,7 +6430,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 32 plantor och 7 vinterståndare inom ca 2 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6478,47 +6463,39 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129894436</v>
+        <v>129894481</v>
       </c>
       <c r="B55" t="n">
-        <v>98833</v>
+        <v>101325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -6529,10 +6506,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493946</v>
+        <v>493990</v>
       </c>
       <c r="R55" t="n">
-        <v>7035738</v>
+        <v>7035652</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6569,7 +6546,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 15 plantor och 3 vinterståndare inom ca 1 m2 yta i äldre hänglavsrik granskog. Marken var snötäckt vid besöket på fyndplatsen. Vid barmark visar sig sannolikt betydligt fler knärotsplantor.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6602,45 +6579,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129894474</v>
+        <v>129894482</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>101325</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493922</v>
+        <v>493912</v>
       </c>
       <c r="R56" t="n">
-        <v>7035751</v>
+        <v>7035578</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6677,7 +6662,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>I ett relativt örtrikt stråk i granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6686,8 +6671,14 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6704,10 +6695,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894426</v>
+        <v>129894483</v>
       </c>
       <c r="B57" t="n">
-        <v>80229</v>
+        <v>101325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,34 +6706,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bratthögarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493924</v>
+        <v>493945</v>
       </c>
       <c r="R57" t="n">
-        <v>7035590</v>
+        <v>7035601</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6777,19 +6776,20 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På barken av en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 51908-2025 artfynd.xlsx
+++ b/artfynd/A 51908-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894454</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894456</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894458</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894459</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894460</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894461</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894462</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894463</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894464</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894465</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894466</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894467</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894468</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2541,6 +2631,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894427</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2659,6 +2754,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894433</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894425</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2917,6 +3022,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894423</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3019,6 +3129,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894439</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894440</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3223,6 +3343,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894441</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3325,6 +3450,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894442</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3427,6 +3557,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894443</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894444</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894445</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3807,6 +3952,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894446</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3946,6 +4096,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894447</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4048,6 +4203,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894448</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4150,6 +4310,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894449</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4252,6 +4417,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894450</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4354,6 +4524,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894451</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4456,6 +4631,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894469</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4558,6 +4738,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894470</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4660,6 +4845,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894471</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4762,6 +4952,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894472</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4864,6 +5059,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894473</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4966,6 +5166,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894474</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5068,6 +5273,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894475</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5170,6 +5380,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894476</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5272,6 +5487,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894477</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5403,6 +5623,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894431</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5505,6 +5730,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894426</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5640,6 +5870,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894428</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5763,6 +5998,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894432</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5887,6 +6127,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894436</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6011,6 +6256,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894437</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6135,6 +6385,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894438</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6242,6 +6497,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894429</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6344,6 +6604,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894479</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6460,6 +6725,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894480</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6576,6 +6846,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894481</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6692,6 +6967,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894482</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6803,8 +7083,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>